--- a/internal_doc/05.测试设计/参数校验/数据同步参数校验.xlsx
+++ b/internal_doc/05.测试设计/参数校验/数据同步参数校验.xlsx
@@ -15,8 +15,147 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="D6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>、取值为</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>的幂次方？</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>------------</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>已确认不是</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>的幂次方，直接是</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>64M</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>到</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>2048M</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>的范围</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>参数项</t>
   </si>
@@ -270,15 +409,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、超过边界值：-1,8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>2、非int类型</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>边界值异常校验不涉及同步，可在cl参数部分验证</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、超过边界值：-2,8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、命名行和配置文件优先级</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -286,7 +429,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,6 +450,26 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -760,10 +923,10 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.625" customWidth="1"/>
-    <col min="2" max="2" width="8.5" customWidth="1"/>
-    <col min="3" max="3" width="29.125" customWidth="1"/>
-    <col min="4" max="4" width="36.875" customWidth="1"/>
-    <col min="5" max="5" width="37.25" customWidth="1"/>
+    <col min="2" max="2" width="3.375" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="25.875" customWidth="1"/>
+    <col min="5" max="5" width="24.5" customWidth="1"/>
     <col min="6" max="6" width="41.875" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
@@ -814,7 +977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="27">
+    <row r="3" spans="1:7">
       <c r="D3" t="s">
         <v>26</v>
       </c>
@@ -847,7 +1010,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="27">
+    <row r="6" spans="1:7">
       <c r="D6" t="s">
         <v>18</v>
       </c>
@@ -858,7 +1021,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="7" customFormat="1" ht="27">
+    <row r="7" spans="1:7" s="7" customFormat="1">
       <c r="F7" s="8" t="s">
         <v>28</v>
       </c>
@@ -1010,10 +1173,10 @@
         <v>24</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="2:7" s="7" customFormat="1">
@@ -1024,7 +1187,7 @@
         <v>63</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -1046,6 +1209,9 @@
       </c>
     </row>
     <row r="24" spans="2:7">
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
       <c r="F24" s="6"/>
     </row>
     <row r="25" spans="2:7">
@@ -1064,6 +1230,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
